--- a/basedatos_partidas/salida/descompuestos/CT-02-06-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-02-06-040.xlsx
@@ -591,10 +591,10 @@
         <v>0.7</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
-        <v>1.82</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="13">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4.22</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="16">
@@ -906,10 +906,10 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>26.51</v>
+        <v>26.23</v>
       </c>
       <c r="H28" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="29">
@@ -925,7 +925,7 @@
       </c>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="5" t="n">
-        <v>26.78</v>
+        <v>26.49</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-02-06-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-02-06-040.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 02 Demoliciones y desmontajes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Escaleras</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
